--- a/Silabus_ELK_Training_V2.xlsx
+++ b/Silabus_ELK_Training_V2.xlsx
@@ -825,7 +825,8 @@
 • Pipeline Aggregations
 • Advanced Aggregations
 • Geo-based Aggregations
-• Aggregations for Visualizing Data in Kibana</t>
+• Visualisasi geo aggregation dengan Kibana Maps
+• Filtered visualization (filter KQL sebelum breakdown) dengan Kibana Lens</t>
         </is>
       </c>
     </row>
